--- a/import-specification/devices/battery.xlsx
+++ b/import-specification/devices/battery.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="163">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="251">
   <si>
     <t>Field Type</t>
   </si>
@@ -41,6 +41,9 @@
     <t>Version</t>
   </si>
   <si>
+    <t>Used For</t>
+  </si>
+  <si>
     <t>configuration</t>
   </si>
   <si>
@@ -140,7 +143,7 @@
     <t>Ah</t>
   </si>
   <si>
-    <t>Nominal capacity</t>
+    <t>Nominal capacity (Only used for small support batteries. Use configuration value for BESS.)</t>
   </si>
   <si>
     <t>B_DOD</t>
@@ -149,7 +152,13 @@
     <t>%</t>
   </si>
   <si>
-    <t>Depth of discharge of a rack</t>
+    <t>Depth of discharge</t>
+  </si>
+  <si>
+    <t>desired</t>
+  </si>
+  <si>
+    <t>Operational Reporting, Age Monitoring</t>
   </si>
   <si>
     <t>B_E_CHARGE_AC</t>
@@ -158,13 +167,28 @@
     <t>kWh</t>
   </si>
   <si>
-    <t>Chargeable Energy</t>
+    <t>Chargeable Energy AC</t>
+  </si>
+  <si>
+    <t>Energy Monitoring</t>
+  </si>
+  <si>
+    <t>B_E_CHARGE_DC</t>
+  </si>
+  <si>
+    <t>Chargeable energy DC</t>
   </si>
   <si>
     <t>B_E_DISCHARGE_AC</t>
   </si>
   <si>
-    <t>Dischargeable Energy</t>
+    <t>Dischargeable Energy AC</t>
+  </si>
+  <si>
+    <t>B_E_DISCHARGE_DC</t>
+  </si>
+  <si>
+    <t>Dischargeable energy DC</t>
   </si>
   <si>
     <t>B_E_EXP</t>
@@ -221,97 +245,511 @@
     <t>Currently stored energy</t>
   </si>
   <si>
+    <t>B_FCE_COUNT</t>
+  </si>
+  <si>
+    <t>FCE count (full cycle equivalent)</t>
+  </si>
+  <si>
+    <t>B_INV_COUNT</t>
+  </si>
+  <si>
+    <t>Number of connected inverters</t>
+  </si>
+  <si>
+    <t>B_I_AC</t>
+  </si>
+  <si>
+    <t>A</t>
+  </si>
+  <si>
+    <t>Battery AC current</t>
+  </si>
+  <si>
+    <t>Safety Monitoring</t>
+  </si>
+  <si>
+    <t>B_I_CELL_MAX[1..x]_[1..x]</t>
+  </si>
+  <si>
+    <t>Maximum cell current</t>
+  </si>
+  <si>
+    <t>B_I_CELL_MAX_CELL_INDEX</t>
+  </si>
+  <si>
+    <t>Index of the cell with the highest cell current</t>
+  </si>
+  <si>
+    <t>B_I_CELL_MAX_MODULE_INDEX</t>
+  </si>
+  <si>
+    <t>Index of the module with the highest cell current</t>
+  </si>
+  <si>
+    <t>B_I_CELL_MAX_RACK_INDEX</t>
+  </si>
+  <si>
+    <t>Index of the rack with the highest cell current</t>
+  </si>
+  <si>
+    <t>B_I_CELL_MIN[1..x]_[1..x]</t>
+  </si>
+  <si>
+    <t>Minimum cell current</t>
+  </si>
+  <si>
+    <t>B_I_CELL_MIN_CELL_INDEX</t>
+  </si>
+  <si>
+    <t>Index of the cell with the lowest cell current</t>
+  </si>
+  <si>
+    <t>B_I_CELL_MIN_MODULE_INDEX</t>
+  </si>
+  <si>
+    <t>Index of the module with the lowest cell current</t>
+  </si>
+  <si>
+    <t>B_I_CELL_MIN_RACK_INDEX</t>
+  </si>
+  <si>
+    <t>Index of the rack with the lowest cell current</t>
+  </si>
+  <si>
+    <t>B_I_DC</t>
+  </si>
+  <si>
+    <t>Battery current DC</t>
+  </si>
+  <si>
+    <t>B_I_DIS_DC</t>
+  </si>
+  <si>
+    <t>Discharging current DC</t>
+  </si>
+  <si>
+    <t>B_LIM_I_CHARGE</t>
+  </si>
+  <si>
+    <t>Maximum charging current</t>
+  </si>
+  <si>
+    <t>B_LIM_I_DISCHARGE</t>
+  </si>
+  <si>
+    <t>Maximum discharging current</t>
+  </si>
+  <si>
+    <t>B_LIM_P_CHARGE</t>
+  </si>
+  <si>
+    <t>W</t>
+  </si>
+  <si>
+    <t>Maximum charging power</t>
+  </si>
+  <si>
+    <t>B_LIM_P_DISCHARGE</t>
+  </si>
+  <si>
+    <t>Maximum discharging power</t>
+  </si>
+  <si>
+    <t>B_LIM_U_CHARGE</t>
+  </si>
+  <si>
+    <t>V</t>
+  </si>
+  <si>
+    <t>Charge end voltage</t>
+  </si>
+  <si>
+    <t>B_LIM_U_DISCHARGE</t>
+  </si>
+  <si>
+    <t>Discharge end voltage</t>
+  </si>
+  <si>
+    <t>B_LOGIC_BAT_COUNT</t>
+  </si>
+  <si>
+    <t>Number of connected logical batteries (combination of racks)</t>
+  </si>
+  <si>
+    <t>B_OT_TOTAL</t>
+  </si>
+  <si>
+    <t>h</t>
+  </si>
+  <si>
+    <t>Operating Hours</t>
+  </si>
+  <si>
+    <t>B_P_DC</t>
+  </si>
+  <si>
+    <t>Total battery power</t>
+  </si>
+  <si>
+    <t>Energy status monitoring</t>
+  </si>
+  <si>
+    <t>B_RECTTIFIER_TOT_I_DC</t>
+  </si>
+  <si>
+    <t>Total current of rectifiers</t>
+  </si>
+  <si>
+    <t>B_RECTTIFIER_TOT_P_DC</t>
+  </si>
+  <si>
+    <t>kW</t>
+  </si>
+  <si>
+    <t>Total battery rectifier dc power</t>
+  </si>
+  <si>
+    <t>B_RECTTIFIER_TOT_U_DC_PCS</t>
+  </si>
+  <si>
+    <t>Total voltage of rectifiers PCS_DC side</t>
+  </si>
+  <si>
+    <t>B_SOC</t>
+  </si>
+  <si>
+    <t>State of Charge</t>
+  </si>
+  <si>
+    <t>B_SOCH</t>
+  </si>
+  <si>
+    <t>State of charge (nominal capacity)</t>
+  </si>
+  <si>
+    <t>B_SOC_CELL_MAX[1..x]_[1..x]</t>
+  </si>
+  <si>
+    <t>Maximum cell state of charge (SoC)</t>
+  </si>
+  <si>
+    <t>B_SOC_CELL_MAX_CELL_INDEX</t>
+  </si>
+  <si>
+    <t>Index of the cell with the highest cell SoC</t>
+  </si>
+  <si>
+    <t>B_SOC_CELL_MAX_MODULE_INDEX</t>
+  </si>
+  <si>
+    <t>Index of the module with the highest cell SoC</t>
+  </si>
+  <si>
+    <t>B_SOC_CELL_MAX_RACK_INDEX</t>
+  </si>
+  <si>
+    <t>Index of the rack with the highest cell SoC</t>
+  </si>
+  <si>
+    <t>B_SOC_CELL_MIN[1..x]_[1..x]</t>
+  </si>
+  <si>
+    <t>Minimum cell state of charge (SoC)</t>
+  </si>
+  <si>
+    <t>B_SOC_CELL_MIN_CELL_INDEX</t>
+  </si>
+  <si>
+    <t>Index of the cell with the lowest cell SoC</t>
+  </si>
+  <si>
+    <t>B_SOC_CELL_MIN_MODULE_INDEX</t>
+  </si>
+  <si>
+    <t>Index of the module with the lowest cell SoC</t>
+  </si>
+  <si>
+    <t>B_SOC_CELL_MIN_RACK_INDEX</t>
+  </si>
+  <si>
+    <t>Index of the rack with the lowest cell SoC</t>
+  </si>
+  <si>
+    <t>B_SOE</t>
+  </si>
+  <si>
+    <t>State of energy of a battery unit</t>
+  </si>
+  <si>
+    <t>monitoring, manage energy trading</t>
+  </si>
+  <si>
+    <t>B_SOH</t>
+  </si>
+  <si>
+    <t>State of health</t>
+  </si>
+  <si>
+    <t>B_T_CELL[1..x]_[1..x]_[1..x]</t>
+  </si>
+  <si>
+    <t>°C</t>
+  </si>
+  <si>
+    <t>Cell temperature  [°C]</t>
+  </si>
+  <si>
+    <t>B_T_CELL_AVG[1..x]_[1..x]</t>
+  </si>
+  <si>
+    <t>Average cell temperature</t>
+  </si>
+  <si>
+    <t>B_T_CELL_MAX[1..x]_[1..x]</t>
+  </si>
+  <si>
+    <t>Maximum cell temperature  [°C]</t>
+  </si>
+  <si>
+    <t>B_T_CELL_MAX_CELL_INDEX</t>
+  </si>
+  <si>
+    <t>Index of the cell with the highest cell temperature</t>
+  </si>
+  <si>
+    <t>B_T_CELL_MAX_MODULE_INDEX</t>
+  </si>
+  <si>
+    <t>Index of the module with the highest cell temperature</t>
+  </si>
+  <si>
+    <t>B_T_CELL_MAX_RACK_INDEX</t>
+  </si>
+  <si>
+    <t>Index of the rack with the highest cell temperature</t>
+  </si>
+  <si>
+    <t>B_T_CELL_MIN[1..x]_[1..x]</t>
+  </si>
+  <si>
+    <t>Minimum cell temperature  [°C]</t>
+  </si>
+  <si>
+    <t>B_T_CELL_MIN_CELL_INDEX</t>
+  </si>
+  <si>
+    <t>Index of the cell with the lowest cell temperature</t>
+  </si>
+  <si>
+    <t>B_T_CELL_MIN_MODULE_INDEX</t>
+  </si>
+  <si>
+    <t>Index of the module with the lowest cell temperature</t>
+  </si>
+  <si>
+    <t>B_T_CELL_MIN_RACK_INDEX</t>
+  </si>
+  <si>
+    <t>Index of the rack with the lowest cell temperature</t>
+  </si>
+  <si>
+    <t>B_T_M[1..x]_[1..x]</t>
+  </si>
+  <si>
+    <t>Module temperature [°C]</t>
+  </si>
+  <si>
+    <t>B_T_M_MAX[1..x]</t>
+  </si>
+  <si>
+    <t>Maximum module temperature [°C]</t>
+  </si>
+  <si>
+    <t>B_T_M_MAX_INDEX_[1-9][0-9]{0,2}</t>
+  </si>
+  <si>
+    <t>Index of the module with the highest temperature in rack X</t>
+  </si>
+  <si>
+    <t>B_T_M_MAX_RACK_INDEX</t>
+  </si>
+  <si>
+    <t>Index of the rack with the highest module temperature</t>
+  </si>
+  <si>
+    <t>B_T_M_MIN[1..x]</t>
+  </si>
+  <si>
+    <t>Minimum module temperature [°C]</t>
+  </si>
+  <si>
+    <t>B_T_M_MIN_INDEX_[1-9][0-9]{0,2}</t>
+  </si>
+  <si>
+    <t>Index of the module with the lowest temperature in rack X</t>
+  </si>
+  <si>
+    <t>B_T_M_MIN_RACK_INDEX</t>
+  </si>
+  <si>
+    <t>Index of the rack with the lowest module temperature</t>
+  </si>
+  <si>
+    <t>B_T_U[1..x]</t>
+  </si>
+  <si>
+    <t>Temperature Outside/ Ambient [°C]</t>
+  </si>
+  <si>
+    <t>B_U_AC</t>
+  </si>
+  <si>
+    <t>Battery AC voltage</t>
+  </si>
+  <si>
+    <t>B_U_BULK</t>
+  </si>
+  <si>
+    <t>Battery charging voltage DC</t>
+  </si>
+  <si>
+    <t>B_U_CELL[1..x]_[1..x]_[1..x]</t>
+  </si>
+  <si>
+    <t>Cell voltage</t>
+  </si>
+  <si>
+    <t>B_U_CELL_AVG</t>
+  </si>
+  <si>
+    <t>Average cell voltage</t>
+  </si>
+  <si>
+    <t>B_U_CELL_MAX[1..x]_[1..x]</t>
+  </si>
+  <si>
+    <t>Maximum cell voltage</t>
+  </si>
+  <si>
+    <t>B_U_CELL_MAX_CELL_INDEX</t>
+  </si>
+  <si>
+    <t>Index of the cell with the highest cell voltage</t>
+  </si>
+  <si>
+    <t>B_U_CELL_MAX_MODULE_INDEX</t>
+  </si>
+  <si>
+    <t>Index of the module with the highest cell voltage</t>
+  </si>
+  <si>
+    <t>B_U_CELL_MAX_RACK_INDEX</t>
+  </si>
+  <si>
+    <t>Index of the rack with the highest cell voltage</t>
+  </si>
+  <si>
+    <t>B_U_CELL_MIN[1..x]_[1..x]</t>
+  </si>
+  <si>
+    <t>Minimum cell voltage</t>
+  </si>
+  <si>
+    <t>B_U_CELL_MIN_CELL_INDEX</t>
+  </si>
+  <si>
+    <t>Index of the cell with the lowest cell voltage</t>
+  </si>
+  <si>
+    <t>B_U_CELL_MIN_MODULE_INDEX</t>
+  </si>
+  <si>
+    <t>Index of the module with the lowest cell voltage</t>
+  </si>
+  <si>
+    <t>B_U_CELL_MIN_RACK_INDEX</t>
+  </si>
+  <si>
+    <t>Index of the rack with the lowest cell voltage</t>
+  </si>
+  <si>
+    <t>B_U_DC</t>
+  </si>
+  <si>
+    <t>Battery voltage</t>
+  </si>
+  <si>
+    <t>B_U_OC</t>
+  </si>
+  <si>
+    <t>Open circuit voltage</t>
+  </si>
+  <si>
+    <t>B_WORKING_M_COUNT</t>
+  </si>
+  <si>
+    <t>Total number of working battery modules in a rack</t>
+  </si>
+  <si>
+    <t>OP_STATE</t>
+  </si>
+  <si>
+    <t>Battery operational state, 1: Disconnected 2: Initializing 3: Connected 4: Standby 5: SOC Protection 6: Suspending 7: Discharging 8: Charging 99: Fault</t>
+  </si>
+  <si>
+    <t>Availability monitoring</t>
+  </si>
+  <si>
+    <t>T[1..x]</t>
+  </si>
+  <si>
+    <t>Temperatures</t>
+  </si>
+  <si>
+    <t>STATE[1..x]</t>
+  </si>
+  <si>
+    <t>Global battery state conditions</t>
+  </si>
+  <si>
+    <t>device event monitoring and alarming</t>
+  </si>
+  <si>
+    <t>ERROR[1..x]</t>
+  </si>
+  <si>
+    <t>Latest battery error code within the interval</t>
+  </si>
+  <si>
+    <t>QS_TX</t>
+  </si>
+  <si>
+    <t>Telegrams transmitted (communication quality)</t>
+  </si>
+  <si>
+    <t>QS_RX</t>
+  </si>
+  <si>
+    <t>Telegrams received (communication quality)</t>
+  </si>
+  <si>
+    <t>deprecated datapoints</t>
+  </si>
+  <si>
     <t>B_F_AC</t>
   </si>
   <si>
     <t>Hz</t>
   </si>
   <si>
-    <t>Grid frequency</t>
-  </si>
-  <si>
-    <t>B_I_AC</t>
-  </si>
-  <si>
-    <t>A</t>
-  </si>
-  <si>
-    <t>Battery AC current</t>
-  </si>
-  <si>
-    <t>B_I_DC</t>
-  </si>
-  <si>
-    <t>Charging current DC</t>
-  </si>
-  <si>
-    <t>B_I_DIS_DC</t>
-  </si>
-  <si>
-    <t>Discharging current DC</t>
-  </si>
-  <si>
-    <t>B_LIM_I_CHARGE</t>
-  </si>
-  <si>
-    <t>Maximum charging current</t>
-  </si>
-  <si>
-    <t>B_LIM_I_DISCHARGE</t>
-  </si>
-  <si>
-    <t>Maximum discharging current</t>
-  </si>
-  <si>
-    <t>B_LIM_P_CHARGE</t>
-  </si>
-  <si>
-    <t>W</t>
-  </si>
-  <si>
-    <t>Maximum charging power</t>
-  </si>
-  <si>
-    <t>B_LIM_P_DISCHARGE</t>
-  </si>
-  <si>
-    <t>Maximum discharging power</t>
-  </si>
-  <si>
-    <t>B_LIM_U_CHARGE</t>
-  </si>
-  <si>
-    <t>V</t>
-  </si>
-  <si>
-    <t>Charge end voltage</t>
-  </si>
-  <si>
-    <t>B_LIM_U_DISCHARGE</t>
-  </si>
-  <si>
-    <t>Discharge end voltage</t>
-  </si>
-  <si>
-    <t>B_OT_TOTAL</t>
-  </si>
-  <si>
-    <t>h</t>
-  </si>
-  <si>
-    <t>Operating Hours</t>
+    <t>Grid frequency, use F_AC on inverter side instead</t>
   </si>
   <si>
     <t>B_P_AC</t>
   </si>
   <si>
-    <t>Battery power AC</t>
-  </si>
-  <si>
-    <t>B_P_DC</t>
-  </si>
-  <si>
-    <t>Total battery power</t>
+    <t>Battery power AC, use P_AC on inverter side instead</t>
   </si>
   <si>
     <t>B_Q_AC</t>
@@ -320,52 +758,7 @@
     <t>var</t>
   </si>
   <si>
-    <t>Battery reactive power AC</t>
-  </si>
-  <si>
-    <t>B_RECTTIFIER_TOT_I_DC</t>
-  </si>
-  <si>
-    <t>Total current of rectifiers</t>
-  </si>
-  <si>
-    <t>B_RECTTIFIER_TOT_P_DC</t>
-  </si>
-  <si>
-    <t>kW</t>
-  </si>
-  <si>
-    <t>Total battery rectifier dc power</t>
-  </si>
-  <si>
-    <t>B_RECTTIFIER_TOT_U_DC_PCS</t>
-  </si>
-  <si>
-    <t>Total voltage of rectifiers PCS_DC side</t>
-  </si>
-  <si>
-    <t>B_SOC</t>
-  </si>
-  <si>
-    <t>State of Charge</t>
-  </si>
-  <si>
-    <t>B_SOCH</t>
-  </si>
-  <si>
-    <t>State of charge (nominal capacity)</t>
-  </si>
-  <si>
-    <t>B_SOE</t>
-  </si>
-  <si>
-    <t>State of energy of a rack</t>
-  </si>
-  <si>
-    <t>B_SOH</t>
-  </si>
-  <si>
-    <t>State of health</t>
+    <t>Battery reactive power AC, use Q_AC on inverter side instead</t>
   </si>
   <si>
     <t>B_S_AC</t>
@@ -374,136 +767,7 @@
     <t>VA</t>
   </si>
   <si>
-    <t>Battery apparent power AC</t>
-  </si>
-  <si>
-    <t>B_T_CELL[1..x]_[1..x]_[1..x]</t>
-  </si>
-  <si>
-    <t>°C</t>
-  </si>
-  <si>
-    <t>Cell temperature  [°C]</t>
-  </si>
-  <si>
-    <t>B_T_CELL_MAX[1..x]_[1..x]</t>
-  </si>
-  <si>
-    <t>Maximum cell temperature  [°C]</t>
-  </si>
-  <si>
-    <t>B_T_CELL_MIN[1..x]_[1..x]</t>
-  </si>
-  <si>
-    <t>Minimum cell temperature  [°C]</t>
-  </si>
-  <si>
-    <t>B_T_M[1..x]_[1..x]</t>
-  </si>
-  <si>
-    <t>Module temperature [°C]</t>
-  </si>
-  <si>
-    <t>B_T_M_MAX[1..x]</t>
-  </si>
-  <si>
-    <t>Maximum module temperature [°C]</t>
-  </si>
-  <si>
-    <t>B_T_M_MIN[1..x]</t>
-  </si>
-  <si>
-    <t>Minimum module temperature [°C]</t>
-  </si>
-  <si>
-    <t>B_T_U[1..x]</t>
-  </si>
-  <si>
-    <t>Temperature Outside/ Ambient [°C]</t>
-  </si>
-  <si>
-    <t>B_U_AC</t>
-  </si>
-  <si>
-    <t>Battery AC voltage</t>
-  </si>
-  <si>
-    <t>B_U_BULK</t>
-  </si>
-  <si>
-    <t>Battery charging voltage DC</t>
-  </si>
-  <si>
-    <t>B_U_CELL[1..x]_[1..x]_[1..x]</t>
-  </si>
-  <si>
-    <t>Cell voltage</t>
-  </si>
-  <si>
-    <t>B_U_CELL_AVG</t>
-  </si>
-  <si>
-    <t>Average cell voltage</t>
-  </si>
-  <si>
-    <t>B_U_CELL_MAX[1..x]_[1..x]</t>
-  </si>
-  <si>
-    <t>Maximum cell voltage</t>
-  </si>
-  <si>
-    <t>B_U_CELL_MIN[1..x]_[1..x]</t>
-  </si>
-  <si>
-    <t>Minimum cell voltage</t>
-  </si>
-  <si>
-    <t>B_U_DC</t>
-  </si>
-  <si>
-    <t>Battery voltage</t>
-  </si>
-  <si>
-    <t>B_U_OC</t>
-  </si>
-  <si>
-    <t>Open circuit voltage</t>
-  </si>
-  <si>
-    <t>B_WORKING_M_COUNT</t>
-  </si>
-  <si>
-    <t>Total number of working battery modules in a rack</t>
-  </si>
-  <si>
-    <t>T[1..x]</t>
-  </si>
-  <si>
-    <t>Temperatures</t>
-  </si>
-  <si>
-    <t>STATE[1..x]</t>
-  </si>
-  <si>
-    <t>Global battery state conditions</t>
-  </si>
-  <si>
-    <t>ERROR[1..x]</t>
-  </si>
-  <si>
-    <t>Global battery error conditions</t>
-  </si>
-  <si>
-    <t>QS_TX</t>
-  </si>
-  <si>
-    <t>Telegrams transmitted (communication quality)</t>
-  </si>
-  <si>
-    <t>QS_RX</t>
-  </si>
-  <si>
-    <t>Telegrams received (communication quality)</t>
+    <t>Battery apparent power AC, use S_AC on inverter side instead</t>
   </si>
 </sst>
 </file>
@@ -855,20 +1119,21 @@
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
   </sheetPr>
-  <dimension ref="A1:H66"/>
+  <dimension ref="A1:I105"/>
   <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col min="1" max="1" width="16.425" bestFit="true" customWidth="true" style="0"/>
-    <col min="2" max="2" width="34.135" bestFit="true" customWidth="true" style="0"/>
+    <col min="1" max="1" width="25.851" bestFit="true" customWidth="true" style="0"/>
+    <col min="2" max="2" width="37.705" bestFit="true" customWidth="true" style="0"/>
     <col min="3" max="3" width="8.141" bestFit="true" customWidth="true" style="0"/>
-    <col min="4" max="4" width="58.843" bestFit="true" customWidth="true" style="0"/>
+    <col min="4" max="4" width="179.242" bestFit="true" customWidth="true" style="0"/>
     <col min="5" max="5" width="9.283" bestFit="true" customWidth="true" style="0"/>
     <col min="6" max="6" width="12.854" bestFit="true" customWidth="true" style="0"/>
     <col min="7" max="7" width="36.42" bestFit="true" customWidth="true" style="0"/>
     <col min="8" max="8" width="11.569" bestFit="true" customWidth="true" style="0"/>
+    <col min="9" max="9" width="44.703" bestFit="true" customWidth="true" style="0"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" s="1" customFormat="1">
+    <row r="1" spans="1:9" s="1" customFormat="1">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -893,665 +1158,725 @@
       <c r="H1" s="1" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="2" spans="1:8">
+      <c r="I1" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9">
       <c r="A2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F2" t="s">
+        <v>12</v>
+      </c>
+      <c r="G2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9">
+      <c r="A3" t="s">
         <v>9</v>
       </c>
-      <c r="D2" t="s">
-        <v>10</v>
-      </c>
-      <c r="F2" t="s">
-        <v>11</v>
-      </c>
-      <c r="G2" t="s">
+      <c r="B3" t="s">
+        <v>15</v>
+      </c>
+      <c r="D3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E3" t="s">
+        <v>17</v>
+      </c>
+      <c r="F3" t="s">
         <v>12</v>
       </c>
-      <c r="H2" t="s">
+      <c r="G3" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="3" spans="1:8">
-      <c r="A3" t="s">
-        <v>8</v>
-      </c>
-      <c r="B3" t="s">
+      <c r="H3" t="s">
         <v>14</v>
       </c>
-      <c r="D3" t="s">
-        <v>15</v>
-      </c>
-      <c r="E3" t="s">
-        <v>16</v>
-      </c>
-      <c r="F3" t="s">
-        <v>11</v>
-      </c>
-      <c r="G3" t="s">
+    </row>
+    <row r="4" spans="1:9">
+      <c r="A4" t="s">
+        <v>9</v>
+      </c>
+      <c r="B4" t="s">
+        <v>18</v>
+      </c>
+      <c r="D4" t="s">
+        <v>19</v>
+      </c>
+      <c r="F4" t="s">
         <v>12</v>
       </c>
-      <c r="H3" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8">
-      <c r="A4" t="s">
-        <v>8</v>
-      </c>
-      <c r="B4" t="s">
-        <v>17</v>
-      </c>
-      <c r="D4" t="s">
-        <v>18</v>
-      </c>
-      <c r="F4" t="s">
-        <v>11</v>
-      </c>
       <c r="G4" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="H4" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9">
       <c r="A5" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B5" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D5" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="G5" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H5" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9">
       <c r="A6" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B6" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D6" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="G6" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="H6" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9">
       <c r="A7" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B7" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D7" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="G7" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="H7" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9">
       <c r="A8" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B8" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D8" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="G8" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="H8" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9">
       <c r="A9" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B9" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D9" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="G9" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="H9" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="10" spans="1:8">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9">
       <c r="A10" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D10" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="G10" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="H10" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="11" spans="1:8">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9">
       <c r="A11" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B11" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C11" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D11" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="12" spans="1:8">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9">
       <c r="A12" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B12" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C12" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="D12" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="13" spans="1:8">
+        <v>45</v>
+      </c>
+      <c r="F12" t="s">
+        <v>46</v>
+      </c>
+      <c r="I12" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9">
       <c r="A13" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B13" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="C13" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="D13" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="14" spans="1:8">
+        <v>50</v>
+      </c>
+      <c r="F13" t="s">
+        <v>46</v>
+      </c>
+      <c r="I13" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9">
       <c r="A14" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B14" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="C14" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="D14" t="s">
+        <v>53</v>
+      </c>
+      <c r="F14" t="s">
+        <v>46</v>
+      </c>
+      <c r="I14" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9">
+      <c r="A15" t="s">
+        <v>39</v>
+      </c>
+      <c r="B15" t="s">
+        <v>54</v>
+      </c>
+      <c r="C15" t="s">
         <v>49</v>
       </c>
-    </row>
-    <row r="15" spans="1:8">
-      <c r="A15" t="s">
-        <v>38</v>
-      </c>
-      <c r="B15" t="s">
-        <v>50</v>
-      </c>
-      <c r="C15" t="s">
-        <v>46</v>
-      </c>
       <c r="D15" t="s">
+        <v>55</v>
+      </c>
+      <c r="F15" t="s">
+        <v>46</v>
+      </c>
+      <c r="I15" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="16" spans="1:8">
+    <row r="16" spans="1:9">
       <c r="A16" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B16" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="C16" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="D16" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="17" spans="1:8">
+        <v>57</v>
+      </c>
+      <c r="F16" t="s">
+        <v>46</v>
+      </c>
+      <c r="I16" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9">
       <c r="A17" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B17" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="C17" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="D17" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="18" spans="1:8">
+        <v>59</v>
+      </c>
+      <c r="F17" t="s">
+        <v>46</v>
+      </c>
+      <c r="I17" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9">
       <c r="A18" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B18" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="C18" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="D18" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="19" spans="1:8">
+        <v>61</v>
+      </c>
+      <c r="F18" t="s">
+        <v>46</v>
+      </c>
+      <c r="I18" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="19" spans="1:9">
       <c r="A19" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B19" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="C19" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="D19" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="20" spans="1:8">
+        <v>63</v>
+      </c>
+      <c r="F19" t="s">
+        <v>46</v>
+      </c>
+      <c r="I19" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="20" spans="1:9">
       <c r="A20" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B20" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="C20" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="D20" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="21" spans="1:8">
+        <v>65</v>
+      </c>
+      <c r="F20" t="s">
+        <v>46</v>
+      </c>
+      <c r="I20" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="21" spans="1:9">
       <c r="A21" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B21" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="C21" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="D21" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="22" spans="1:8">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="22" spans="1:9">
       <c r="A22" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B22" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="C22" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="D22" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="23" spans="1:8">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="23" spans="1:9">
       <c r="A23" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B23" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="C23" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="D23" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="24" spans="1:8">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="24" spans="1:9">
       <c r="A24" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B24" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="C24" t="s">
-        <v>69</v>
+        <v>49</v>
       </c>
       <c r="D24" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="25" spans="1:8">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="25" spans="1:9">
       <c r="A25" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B25" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="C25" t="s">
-        <v>72</v>
+        <v>49</v>
       </c>
       <c r="D25" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="26" spans="1:8">
+        <v>75</v>
+      </c>
+      <c r="F25" t="s">
+        <v>46</v>
+      </c>
+      <c r="I25" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="26" spans="1:9">
       <c r="A26" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B26" t="s">
-        <v>74</v>
-      </c>
-      <c r="C26" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="D26" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="27" spans="1:8">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="27" spans="1:9">
       <c r="A27" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B27" t="s">
-        <v>76</v>
-      </c>
-      <c r="C27" t="s">
-        <v>72</v>
+        <v>78</v>
       </c>
       <c r="D27" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="28" spans="1:8">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="28" spans="1:9">
       <c r="A28" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B28" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="C28" t="s">
-        <v>72</v>
+        <v>81</v>
       </c>
       <c r="D28" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="29" spans="1:8">
+        <v>82</v>
+      </c>
+      <c r="F28" t="s">
+        <v>46</v>
+      </c>
+      <c r="I28" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="29" spans="1:9">
       <c r="A29" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B29" t="s">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="C29" t="s">
-        <v>72</v>
+        <v>81</v>
       </c>
       <c r="D29" t="s">
+        <v>85</v>
+      </c>
+      <c r="F29" t="s">
+        <v>46</v>
+      </c>
+      <c r="I29" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="30" spans="1:9">
+      <c r="A30" t="s">
+        <v>39</v>
+      </c>
+      <c r="B30" t="s">
+        <v>86</v>
+      </c>
+      <c r="D30" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="31" spans="1:9">
+      <c r="A31" t="s">
+        <v>39</v>
+      </c>
+      <c r="B31" t="s">
+        <v>88</v>
+      </c>
+      <c r="D31" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="32" spans="1:9">
+      <c r="A32" t="s">
+        <v>39</v>
+      </c>
+      <c r="B32" t="s">
+        <v>90</v>
+      </c>
+      <c r="D32" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="33" spans="1:9">
+      <c r="A33" t="s">
+        <v>39</v>
+      </c>
+      <c r="B33" t="s">
+        <v>92</v>
+      </c>
+      <c r="C33" t="s">
         <v>81</v>
       </c>
-    </row>
-    <row r="30" spans="1:8">
-      <c r="A30" t="s">
-        <v>38</v>
-      </c>
-      <c r="B30" t="s">
-        <v>82</v>
-      </c>
-      <c r="C30" t="s">
+      <c r="D33" t="s">
+        <v>93</v>
+      </c>
+      <c r="F33" t="s">
+        <v>46</v>
+      </c>
+      <c r="I33" t="s">
         <v>83</v>
       </c>
-      <c r="D30" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="31" spans="1:8">
-      <c r="A31" t="s">
-        <v>38</v>
-      </c>
-      <c r="B31" t="s">
-        <v>85</v>
-      </c>
-      <c r="C31" t="s">
-        <v>83</v>
-      </c>
-      <c r="D31" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="32" spans="1:8">
-      <c r="A32" t="s">
-        <v>38</v>
-      </c>
-      <c r="B32" t="s">
-        <v>87</v>
-      </c>
-      <c r="C32" t="s">
-        <v>88</v>
-      </c>
-      <c r="D32" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="33" spans="1:8">
-      <c r="A33" t="s">
-        <v>38</v>
-      </c>
-      <c r="B33" t="s">
-        <v>90</v>
-      </c>
-      <c r="C33" t="s">
-        <v>88</v>
-      </c>
-      <c r="D33" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="34" spans="1:8">
+    </row>
+    <row r="34" spans="1:9">
       <c r="A34" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B34" t="s">
-        <v>92</v>
-      </c>
-      <c r="C34" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="D34" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="35" spans="1:8">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="35" spans="1:9">
       <c r="A35" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B35" t="s">
-        <v>95</v>
-      </c>
-      <c r="C35" t="s">
-        <v>83</v>
+        <v>96</v>
       </c>
       <c r="D35" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="36" spans="1:8">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="36" spans="1:9">
       <c r="A36" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B36" t="s">
-        <v>97</v>
-      </c>
-      <c r="C36" t="s">
-        <v>83</v>
+        <v>98</v>
       </c>
       <c r="D36" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="37" spans="1:8">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="37" spans="1:9">
       <c r="A37" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B37" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C37" t="s">
-        <v>100</v>
+        <v>81</v>
       </c>
       <c r="D37" t="s">
         <v>101</v>
       </c>
-    </row>
-    <row r="38" spans="1:8">
+      <c r="F37" t="s">
+        <v>46</v>
+      </c>
+      <c r="I37" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="38" spans="1:9">
       <c r="A38" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B38" t="s">
         <v>102</v>
       </c>
       <c r="C38" t="s">
-        <v>72</v>
+        <v>81</v>
       </c>
       <c r="D38" t="s">
         <v>103</v>
       </c>
     </row>
-    <row r="39" spans="1:8">
+    <row r="39" spans="1:9">
       <c r="A39" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B39" t="s">
         <v>104</v>
       </c>
       <c r="C39" t="s">
+        <v>81</v>
+      </c>
+      <c r="D39" t="s">
         <v>105</v>
       </c>
-      <c r="D39" t="s">
+    </row>
+    <row r="40" spans="1:9">
+      <c r="A40" t="s">
+        <v>39</v>
+      </c>
+      <c r="B40" t="s">
         <v>106</v>
       </c>
-    </row>
-    <row r="40" spans="1:8">
-      <c r="A40" t="s">
-        <v>38</v>
-      </c>
-      <c r="B40" t="s">
+      <c r="C40" t="s">
+        <v>81</v>
+      </c>
+      <c r="D40" t="s">
         <v>107</v>
       </c>
-      <c r="C40" t="s">
-        <v>88</v>
-      </c>
-      <c r="D40" t="s">
+    </row>
+    <row r="41" spans="1:9">
+      <c r="A41" t="s">
+        <v>39</v>
+      </c>
+      <c r="B41" t="s">
         <v>108</v>
       </c>
-    </row>
-    <row r="41" spans="1:8">
-      <c r="A41" t="s">
-        <v>38</v>
-      </c>
-      <c r="B41" t="s">
+      <c r="C41" t="s">
         <v>109</v>
-      </c>
-      <c r="C41" t="s">
-        <v>43</v>
       </c>
       <c r="D41" t="s">
         <v>110</v>
       </c>
     </row>
-    <row r="42" spans="1:8">
+    <row r="42" spans="1:9">
       <c r="A42" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B42" t="s">
         <v>111</v>
       </c>
       <c r="C42" t="s">
-        <v>43</v>
+        <v>109</v>
       </c>
       <c r="D42" t="s">
         <v>112</v>
       </c>
     </row>
-    <row r="43" spans="1:8">
+    <row r="43" spans="1:9">
       <c r="A43" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B43" t="s">
         <v>113</v>
       </c>
       <c r="C43" t="s">
-        <v>43</v>
+        <v>114</v>
       </c>
       <c r="D43" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="44" spans="1:9">
+      <c r="A44" t="s">
+        <v>39</v>
+      </c>
+      <c r="B44" t="s">
+        <v>116</v>
+      </c>
+      <c r="C44" t="s">
         <v>114</v>
       </c>
-    </row>
-    <row r="44" spans="1:8">
-      <c r="A44" t="s">
-        <v>38</v>
-      </c>
-      <c r="B44" t="s">
-        <v>115</v>
-      </c>
-      <c r="C44" t="s">
-        <v>43</v>
-      </c>
       <c r="D44" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="45" spans="1:8">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="45" spans="1:9">
       <c r="A45" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B45" t="s">
-        <v>117</v>
-      </c>
-      <c r="C45" t="s">
         <v>118</v>
       </c>
       <c r="D45" t="s">
         <v>119</v>
       </c>
     </row>
-    <row r="46" spans="1:8">
+    <row r="46" spans="1:9">
       <c r="A46" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B46" t="s">
         <v>120</v>
@@ -1563,269 +1888,857 @@
         <v>122</v>
       </c>
     </row>
-    <row r="47" spans="1:8">
+    <row r="47" spans="1:9">
       <c r="A47" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B47" t="s">
         <v>123</v>
       </c>
       <c r="C47" t="s">
-        <v>121</v>
+        <v>109</v>
       </c>
       <c r="D47" t="s">
         <v>124</v>
       </c>
-    </row>
-    <row r="48" spans="1:8">
+      <c r="F47" t="s">
+        <v>46</v>
+      </c>
+      <c r="I47" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="48" spans="1:9">
       <c r="A48" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B48" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="C48" t="s">
-        <v>121</v>
+        <v>81</v>
       </c>
       <c r="D48" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="49" spans="1:8">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="49" spans="1:9">
       <c r="A49" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B49" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="C49" t="s">
-        <v>121</v>
+        <v>129</v>
       </c>
       <c r="D49" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="50" spans="1:8">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="50" spans="1:9">
       <c r="A50" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B50" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="C50" t="s">
-        <v>121</v>
+        <v>114</v>
       </c>
       <c r="D50" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="51" spans="1:8">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="51" spans="1:9">
       <c r="A51" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B51" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="C51" t="s">
-        <v>121</v>
+        <v>44</v>
       </c>
       <c r="D51" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="52" spans="1:8">
+        <v>134</v>
+      </c>
+      <c r="F51" t="s">
+        <v>12</v>
+      </c>
+      <c r="I51" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="52" spans="1:9">
       <c r="A52" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B52" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="C52" t="s">
-        <v>121</v>
+        <v>44</v>
       </c>
       <c r="D52" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="53" spans="1:8">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="53" spans="1:9">
       <c r="A53" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B53" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="C53" t="s">
-        <v>88</v>
+        <v>44</v>
       </c>
       <c r="D53" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="54" spans="1:8">
+        <v>138</v>
+      </c>
+      <c r="I53" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="54" spans="1:9">
       <c r="A54" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B54" t="s">
-        <v>137</v>
-      </c>
-      <c r="C54" t="s">
-        <v>88</v>
+        <v>139</v>
       </c>
       <c r="D54" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="55" spans="1:8">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="55" spans="1:9">
       <c r="A55" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B55" t="s">
-        <v>139</v>
-      </c>
-      <c r="C55" t="s">
-        <v>88</v>
+        <v>141</v>
       </c>
       <c r="D55" t="s">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="56" spans="1:8">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="56" spans="1:9">
       <c r="A56" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B56" t="s">
-        <v>141</v>
-      </c>
-      <c r="C56" t="s">
-        <v>88</v>
+        <v>143</v>
       </c>
       <c r="D56" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="57" spans="1:8">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="57" spans="1:9">
       <c r="A57" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B57" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="C57" t="s">
-        <v>88</v>
+        <v>44</v>
       </c>
       <c r="D57" t="s">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="58" spans="1:8">
+        <v>146</v>
+      </c>
+      <c r="I57" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="58" spans="1:9">
       <c r="A58" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B58" t="s">
-        <v>145</v>
-      </c>
-      <c r="C58" t="s">
-        <v>88</v>
+        <v>147</v>
       </c>
       <c r="D58" t="s">
-        <v>146</v>
-      </c>
-    </row>
-    <row r="59" spans="1:8">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="59" spans="1:9">
       <c r="A59" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B59" t="s">
-        <v>147</v>
-      </c>
-      <c r="C59" t="s">
-        <v>88</v>
+        <v>149</v>
       </c>
       <c r="D59" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="60" spans="1:8">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="60" spans="1:9">
       <c r="A60" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B60" t="s">
-        <v>149</v>
-      </c>
-      <c r="C60" t="s">
-        <v>88</v>
+        <v>151</v>
       </c>
       <c r="D60" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="61" spans="1:8">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="61" spans="1:9">
       <c r="A61" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B61" t="s">
-        <v>151</v>
+        <v>153</v>
+      </c>
+      <c r="C61" t="s">
+        <v>44</v>
       </c>
       <c r="D61" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="62" spans="1:8">
+        <v>154</v>
+      </c>
+      <c r="I61" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="62" spans="1:9">
       <c r="A62" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B62" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="C62" t="s">
-        <v>121</v>
+        <v>44</v>
       </c>
       <c r="D62" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="63" spans="1:8">
+        <v>157</v>
+      </c>
+      <c r="F62" t="s">
+        <v>46</v>
+      </c>
+      <c r="I62" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="63" spans="1:9">
       <c r="A63" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B63" t="s">
-        <v>155</v>
+        <v>158</v>
+      </c>
+      <c r="C63" t="s">
+        <v>159</v>
       </c>
       <c r="D63" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="64" spans="1:8">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="64" spans="1:9">
       <c r="A64" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B64" t="s">
-        <v>157</v>
+        <v>161</v>
+      </c>
+      <c r="C64" t="s">
+        <v>159</v>
       </c>
       <c r="D64" t="s">
-        <v>158</v>
-      </c>
-    </row>
-    <row r="65" spans="1:8">
+        <v>162</v>
+      </c>
+      <c r="F64" t="s">
+        <v>46</v>
+      </c>
+      <c r="I64" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="65" spans="1:9">
       <c r="A65" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B65" t="s">
+        <v>163</v>
+      </c>
+      <c r="C65" t="s">
         <v>159</v>
       </c>
       <c r="D65" t="s">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="66" spans="1:8">
+        <v>164</v>
+      </c>
+      <c r="F65" t="s">
+        <v>46</v>
+      </c>
+      <c r="I65" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="66" spans="1:9">
       <c r="A66" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B66" t="s">
-        <v>161</v>
+        <v>165</v>
       </c>
       <c r="D66" t="s">
-        <v>162</v>
+        <v>166</v>
+      </c>
+    </row>
+    <row r="67" spans="1:9">
+      <c r="A67" t="s">
+        <v>39</v>
+      </c>
+      <c r="B67" t="s">
+        <v>167</v>
+      </c>
+      <c r="D67" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="68" spans="1:9">
+      <c r="A68" t="s">
+        <v>39</v>
+      </c>
+      <c r="B68" t="s">
+        <v>169</v>
+      </c>
+      <c r="D68" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="69" spans="1:9">
+      <c r="A69" t="s">
+        <v>39</v>
+      </c>
+      <c r="B69" t="s">
+        <v>171</v>
+      </c>
+      <c r="C69" t="s">
+        <v>159</v>
+      </c>
+      <c r="D69" t="s">
+        <v>172</v>
+      </c>
+      <c r="F69" t="s">
+        <v>46</v>
+      </c>
+      <c r="I69" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="70" spans="1:9">
+      <c r="A70" t="s">
+        <v>39</v>
+      </c>
+      <c r="B70" t="s">
+        <v>173</v>
+      </c>
+      <c r="D70" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="71" spans="1:9">
+      <c r="A71" t="s">
+        <v>39</v>
+      </c>
+      <c r="B71" t="s">
+        <v>175</v>
+      </c>
+      <c r="D71" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="72" spans="1:9">
+      <c r="A72" t="s">
+        <v>39</v>
+      </c>
+      <c r="B72" t="s">
+        <v>177</v>
+      </c>
+      <c r="D72" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="73" spans="1:9">
+      <c r="A73" t="s">
+        <v>39</v>
+      </c>
+      <c r="B73" t="s">
+        <v>179</v>
+      </c>
+      <c r="C73" t="s">
+        <v>159</v>
+      </c>
+      <c r="D73" t="s">
+        <v>180</v>
+      </c>
+      <c r="F73" t="s">
+        <v>46</v>
+      </c>
+      <c r="I73" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="74" spans="1:9">
+      <c r="A74" t="s">
+        <v>39</v>
+      </c>
+      <c r="B74" t="s">
+        <v>181</v>
+      </c>
+      <c r="C74" t="s">
+        <v>159</v>
+      </c>
+      <c r="D74" t="s">
+        <v>182</v>
+      </c>
+      <c r="F74" t="s">
+        <v>46</v>
+      </c>
+      <c r="I74" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="75" spans="1:9">
+      <c r="A75" t="s">
+        <v>39</v>
+      </c>
+      <c r="B75" t="s">
+        <v>183</v>
+      </c>
+      <c r="D75" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="76" spans="1:9">
+      <c r="A76" t="s">
+        <v>39</v>
+      </c>
+      <c r="B76" t="s">
+        <v>185</v>
+      </c>
+      <c r="D76" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="77" spans="1:9">
+      <c r="A77" t="s">
+        <v>39</v>
+      </c>
+      <c r="B77" t="s">
+        <v>187</v>
+      </c>
+      <c r="C77" t="s">
+        <v>159</v>
+      </c>
+      <c r="D77" t="s">
+        <v>188</v>
+      </c>
+      <c r="F77" t="s">
+        <v>46</v>
+      </c>
+      <c r="I77" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="78" spans="1:9">
+      <c r="A78" t="s">
+        <v>39</v>
+      </c>
+      <c r="B78" t="s">
+        <v>189</v>
+      </c>
+      <c r="D78" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="79" spans="1:9">
+      <c r="A79" t="s">
+        <v>39</v>
+      </c>
+      <c r="B79" t="s">
+        <v>191</v>
+      </c>
+      <c r="D79" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="80" spans="1:9">
+      <c r="A80" t="s">
+        <v>39</v>
+      </c>
+      <c r="B80" t="s">
+        <v>193</v>
+      </c>
+      <c r="C80" t="s">
+        <v>159</v>
+      </c>
+      <c r="D80" t="s">
+        <v>194</v>
+      </c>
+      <c r="F80" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="81" spans="1:9">
+      <c r="A81" t="s">
+        <v>39</v>
+      </c>
+      <c r="B81" t="s">
+        <v>195</v>
+      </c>
+      <c r="C81" t="s">
+        <v>114</v>
+      </c>
+      <c r="D81" t="s">
+        <v>196</v>
+      </c>
+      <c r="F81" t="s">
+        <v>46</v>
+      </c>
+      <c r="I81" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="82" spans="1:9">
+      <c r="A82" t="s">
+        <v>39</v>
+      </c>
+      <c r="B82" t="s">
+        <v>197</v>
+      </c>
+      <c r="C82" t="s">
+        <v>114</v>
+      </c>
+      <c r="D82" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="83" spans="1:9">
+      <c r="A83" t="s">
+        <v>39</v>
+      </c>
+      <c r="B83" t="s">
+        <v>199</v>
+      </c>
+      <c r="C83" t="s">
+        <v>114</v>
+      </c>
+      <c r="D83" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="84" spans="1:9">
+      <c r="A84" t="s">
+        <v>39</v>
+      </c>
+      <c r="B84" t="s">
+        <v>201</v>
+      </c>
+      <c r="C84" t="s">
+        <v>114</v>
+      </c>
+      <c r="D84" t="s">
+        <v>202</v>
+      </c>
+      <c r="F84" t="s">
+        <v>46</v>
+      </c>
+      <c r="I84" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="85" spans="1:9">
+      <c r="A85" t="s">
+        <v>39</v>
+      </c>
+      <c r="B85" t="s">
+        <v>203</v>
+      </c>
+      <c r="C85" t="s">
+        <v>114</v>
+      </c>
+      <c r="D85" t="s">
+        <v>204</v>
+      </c>
+      <c r="F85" t="s">
+        <v>46</v>
+      </c>
+      <c r="I85" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="86" spans="1:9">
+      <c r="A86" t="s">
+        <v>39</v>
+      </c>
+      <c r="B86" t="s">
+        <v>205</v>
+      </c>
+      <c r="D86" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="87" spans="1:9">
+      <c r="A87" t="s">
+        <v>39</v>
+      </c>
+      <c r="B87" t="s">
+        <v>207</v>
+      </c>
+      <c r="D87" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="88" spans="1:9">
+      <c r="A88" t="s">
+        <v>39</v>
+      </c>
+      <c r="B88" t="s">
+        <v>209</v>
+      </c>
+      <c r="D88" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="89" spans="1:9">
+      <c r="A89" t="s">
+        <v>39</v>
+      </c>
+      <c r="B89" t="s">
+        <v>211</v>
+      </c>
+      <c r="C89" t="s">
+        <v>114</v>
+      </c>
+      <c r="D89" t="s">
+        <v>212</v>
+      </c>
+      <c r="F89" t="s">
+        <v>46</v>
+      </c>
+      <c r="I89" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="90" spans="1:9">
+      <c r="A90" t="s">
+        <v>39</v>
+      </c>
+      <c r="B90" t="s">
+        <v>213</v>
+      </c>
+      <c r="D90" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="91" spans="1:9">
+      <c r="A91" t="s">
+        <v>39</v>
+      </c>
+      <c r="B91" t="s">
+        <v>215</v>
+      </c>
+      <c r="D91" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="92" spans="1:9">
+      <c r="A92" t="s">
+        <v>39</v>
+      </c>
+      <c r="B92" t="s">
+        <v>217</v>
+      </c>
+      <c r="D92" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="93" spans="1:9">
+      <c r="A93" t="s">
+        <v>39</v>
+      </c>
+      <c r="B93" t="s">
+        <v>219</v>
+      </c>
+      <c r="C93" t="s">
+        <v>114</v>
+      </c>
+      <c r="D93" t="s">
+        <v>220</v>
+      </c>
+      <c r="F93" t="s">
+        <v>46</v>
+      </c>
+      <c r="I93" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="94" spans="1:9">
+      <c r="A94" t="s">
+        <v>39</v>
+      </c>
+      <c r="B94" t="s">
+        <v>221</v>
+      </c>
+      <c r="C94" t="s">
+        <v>114</v>
+      </c>
+      <c r="D94" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="95" spans="1:9">
+      <c r="A95" t="s">
+        <v>39</v>
+      </c>
+      <c r="B95" t="s">
+        <v>223</v>
+      </c>
+      <c r="D95" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="96" spans="1:9">
+      <c r="A96" t="s">
+        <v>39</v>
+      </c>
+      <c r="B96" t="s">
+        <v>225</v>
+      </c>
+      <c r="D96" t="s">
+        <v>226</v>
+      </c>
+      <c r="F96" t="s">
+        <v>46</v>
+      </c>
+      <c r="I96" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="97" spans="1:9">
+      <c r="A97" t="s">
+        <v>39</v>
+      </c>
+      <c r="B97" t="s">
+        <v>228</v>
+      </c>
+      <c r="C97" t="s">
+        <v>159</v>
+      </c>
+      <c r="D97" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="98" spans="1:9">
+      <c r="A98" t="s">
+        <v>39</v>
+      </c>
+      <c r="B98" t="s">
+        <v>230</v>
+      </c>
+      <c r="D98" t="s">
+        <v>231</v>
+      </c>
+      <c r="F98" t="s">
+        <v>46</v>
+      </c>
+      <c r="I98" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="99" spans="1:9">
+      <c r="A99" t="s">
+        <v>39</v>
+      </c>
+      <c r="B99" t="s">
+        <v>233</v>
+      </c>
+      <c r="D99" t="s">
+        <v>234</v>
+      </c>
+      <c r="I99" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="100" spans="1:9">
+      <c r="A100" t="s">
+        <v>39</v>
+      </c>
+      <c r="B100" t="s">
+        <v>235</v>
+      </c>
+      <c r="D100" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="101" spans="1:9">
+      <c r="A101" t="s">
+        <v>39</v>
+      </c>
+      <c r="B101" t="s">
+        <v>237</v>
+      </c>
+      <c r="D101" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="102" spans="1:9">
+      <c r="A102" t="s">
+        <v>239</v>
+      </c>
+      <c r="B102" t="s">
+        <v>240</v>
+      </c>
+      <c r="C102" t="s">
+        <v>241</v>
+      </c>
+      <c r="D102" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="103" spans="1:9">
+      <c r="A103" t="s">
+        <v>239</v>
+      </c>
+      <c r="B103" t="s">
+        <v>243</v>
+      </c>
+      <c r="C103" t="s">
+        <v>109</v>
+      </c>
+      <c r="D103" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="104" spans="1:9">
+      <c r="A104" t="s">
+        <v>239</v>
+      </c>
+      <c r="B104" t="s">
+        <v>245</v>
+      </c>
+      <c r="C104" t="s">
+        <v>246</v>
+      </c>
+      <c r="D104" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="105" spans="1:9">
+      <c r="A105" t="s">
+        <v>239</v>
+      </c>
+      <c r="B105" t="s">
+        <v>248</v>
+      </c>
+      <c r="C105" t="s">
+        <v>249</v>
+      </c>
+      <c r="D105" t="s">
+        <v>250</v>
       </c>
     </row>
   </sheetData>
